--- a/client/dist/Sorce/balanceKR.xlsx
+++ b/client/dist/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 09.02.2025 14:55:13</t>
+    <t>Период: на 23.12.2025 16:15:15</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,22 +62,49 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт</t>
-  </si>
-  <si>
-    <t>Желе вишня УБ 78г /56шт</t>
+    <t>Желе ананас УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт</t>
-  </si>
-  <si>
-    <t>Какао-порошок 100г/40 УБ</t>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Какао-порошок 22% УБ 60г /26шт</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 80г /48шт</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 80г /48шт АКЦІЯ</t>
   </si>
   <si>
     <t>ДОБАВКИ</t>
@@ -89,49 +116,88 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
-    <t>Ванільний цукор УБ 40г /45шт</t>
+    <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желатин УБ 25г /42шт</t>
   </si>
   <si>
+    <t>Желатин УБ 25г /42шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт /</t>
+  </si>
+  <si>
+    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
-    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Прованські трави УБ 10г /28шт</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт</t>
+    <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Суміш зелені УБ 10г /24шт</t>
+  </si>
+  <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
@@ -143,7 +209,13 @@
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт</t>
+    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /</t>
+  </si>
+  <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>СПЕЦІЇ</t>
@@ -170,7 +242,7 @@
     <t>Паприка мелена УБ 20г /34шт</t>
   </si>
   <si>
-    <t>Перець духм"яний УБ 20г /22шт</t>
+    <t>Перець духмяний УБ 15г /30шт</t>
   </si>
   <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
@@ -182,6 +254,12 @@
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
@@ -194,46 +272,61 @@
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт ДС</t>
-  </si>
-  <si>
-    <t>БАТОН ROSHEN з начинкою 43г/180</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г/180 шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон мол-шок карамель 40г/180/30</t>
-  </si>
-  <si>
-    <t>Батон мол-шок крем-брюле 43г/180/30</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>БІСКВІТИ</t>
@@ -245,6 +338,9 @@
     <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
+  </si>
+  <si>
     <t>Бісквіт Рошен Празький ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -263,12 +359,21 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -278,9 +383,6 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
-  </si>
-  <si>
     <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
   </si>
   <si>
@@ -293,12 +395,24 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -326,24 +440,27 @@
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ВКФ 72г /22шт AR /</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers какао-молоко ККФ 216г /16шт</t>
   </si>
   <si>
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ВКФ 72г /22шт AR /</t>
-  </si>
-  <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers молоко ВКФ 216г /16шт</t>
+  </si>
+  <si>
+    <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -362,9 +479,6 @@
     <t>Beri РЦ 180г /12шт</t>
   </si>
   <si>
-    <t>Beri РЦ 180г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Bonny-Fruit літній мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
@@ -380,27 +494,33 @@
     <t>Milky Splash РЦ 150г /12пак</t>
   </si>
   <si>
-    <t>Milky Splash РЦ 150г /12пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Mintex+ Berry зі смаком лісових ягід та ментолу ВКФ 140г /15шт</t>
   </si>
   <si>
     <t>Mintex+ Lemon зі смаком лимону та ментолу ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Mintex+ зі смаком м'яти ВКФ 140г /15шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -410,7 +530,7 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
@@ -419,7 +539,7 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
@@ -428,46 +548,97 @@
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
@@ -485,6 +656,12 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -494,6 +671,9 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -515,7 +695,7 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
@@ -524,18 +704,30 @@
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -563,25 +755,25 @@
     <t>Шалена бджілка ВКФ 200г /12шт</t>
   </si>
   <si>
+    <t>Шалена бджілка РЦ 200г /12шт</t>
+  </si>
+  <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
   </si>
   <si>
-    <t>Beri РЦ 1кг /8пак</t>
-  </si>
-  <si>
     <t>Beri РЦ 1кг /8пак /</t>
   </si>
   <si>
+    <t>Coconut КрКФ 1кг /7пак</t>
+  </si>
+  <si>
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>CoffeeLike ВКФ 1кг /7пак /</t>
-  </si>
-  <si>
     <t>CoffeeLike КрКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Fudgenta ВКФ 0.785кг /9пак</t>
+    <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
@@ -590,6 +782,9 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
+  </si>
+  <si>
     <t>Lollipops GUM Cola КрКФ 0.92кг /9шт</t>
   </si>
   <si>
@@ -599,6 +794,9 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
+    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -647,9 +845,6 @@
     <t>Карамелькино КрКФ 1кг /8пак /</t>
   </si>
   <si>
-    <t>Молочна крапля ВКФ 1кг /7пак</t>
-  </si>
-  <si>
     <t>Молочна крапля ВКФ 1кг /7пак /</t>
   </si>
   <si>
@@ -662,9 +857,6 @@
     <t>Рошен джус мікс РЦ 1кг /8пак /</t>
   </si>
   <si>
-    <t>Рошен евкаліпт-ментол КрКФ 1кг /8пак /</t>
-  </si>
-  <si>
     <t>Цитрусовий мікс РЦ 1кг /7пак /</t>
   </si>
   <si>
@@ -686,10 +878,7 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт</t>
-  </si>
-  <si>
-    <t>Cherry Queen heart РЦ 122г /8шт ДС</t>
+    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
@@ -707,6 +896,9 @@
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
+    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -716,13 +908,13 @@
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
-    <t>Київ вечірній ККФ 176г /7шт</t>
-  </si>
-  <si>
-    <t>Київ вечірній ККФ 352г /7шт</t>
-  </si>
-  <si>
-    <t>Київ вечірній Новий Рік ККФ 176г /7шт</t>
+    <t>Київ вечірній ВКФ 176г /7шт</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
     <t>Стріла Подільска 200г/10</t>
@@ -731,6 +923,39 @@
     <t>ПЕЧИВО ТА КРЕКЕР ФАСОВАНІ</t>
   </si>
   <si>
+    <t>2 CRACK з молочно-ванільною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Brownie з какао ККФ 152г /21шт</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
@@ -752,18 +977,15 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 135г /21шт /</t>
-  </si>
-  <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -779,6 +1001,12 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
+  </si>
+  <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -794,27 +1022,30 @@
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою 180г/28</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою вишня-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою какао 180г/28</t>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт</t>
+    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
   </si>
   <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Multicake з начинкою чорниця-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -827,63 +1058,108 @@
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
-  </si>
-  <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт UA</t>
-  </si>
-  <si>
-    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
-  </si>
-  <si>
-    <t>КРЕКЕР 2 CRACK з шоколадною начинкою ККФ 235г /14шт</t>
+    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>ПОДАРУНКИ</t>
+  </si>
+  <si>
+    <t>ПОДАРУНКИ 2026</t>
+  </si>
+  <si>
+    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №6 26 Веселе свято РЦ 458г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
   </si>
   <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
-    <t>Candy Nut м"яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+    <t>Boo! Bear РЦ 1кг /5пак</t>
+  </si>
+  <si>
+    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+  </si>
+  <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Hola! Granola РЦ 0.5кг /8пак</t>
-  </si>
-  <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт /</t>
+    <t>Flaksi какао ККФ 0.5кг /8пак</t>
   </si>
   <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт /</t>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
+    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
+  </si>
+  <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+  </si>
+  <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Sorrento ВКФ 2кг /5пак</t>
+    <t>Krock з арахісом ВКФ 1кг /8пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Milaxy ВКФ 1кг /4пак</t>
+  </si>
+  <si>
+    <t>Sorrento ВКФ 1кг /9пак</t>
   </si>
   <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -899,10 +1175,13 @@
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 2кг /5пак АКЦІЯ</t>
+    <t>Ромашка ВКФ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
@@ -911,19 +1190,25 @@
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 350г /12шт PL</t>
-  </si>
-  <si>
-    <t>Johnny Krocker milk ВКФ 350г /12шт /</t>
-  </si>
-  <si>
-    <t>Монблан РЦ 240г /15шт</t>
+    <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
+  </si>
+  <si>
+    <t>Johnny Krocker milk ВКФ 350г /12шт PL</t>
   </si>
   <si>
     <t>Монблан РЦ 240г /15шт /</t>
@@ -932,127 +1217,169 @@
     <t>ШОКОЛАД</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
+  </si>
+  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочный ВКФ 260г /15шт</t>
-  </si>
-  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
-  </si>
-  <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /24шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний ВКФ 90г /24шт /</t>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з сезамом ВКФ 90г /24шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /17шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 290г /12шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ</t>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
@@ -1067,46 +1394,43 @@
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen екстрачорний+ціл.л.горіх 90г/18 FP</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP /</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦІЯ</t>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
+  </si>
+  <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
@@ -1115,16 +1439,46 @@
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
+  </si>
+  <si>
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
   <si>
+    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>ФІГУРКИ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen зимовий ВКФ 100г /12шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1351,6 +1705,12 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1370,7 +1730,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C369"/>
+  <dimension ref="C487"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1435,7 +1795,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>641</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1443,7 +1803,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>377927</v>
+        <v>453025</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1451,7 +1811,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>32215</v>
+        <v>84079</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1459,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>4773</v>
+        <v>7697</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1467,7 +1827,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>396</v>
+        <v>727</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1475,15 +1835,15 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>812</v>
+        <v>912</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
       <c r="B17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="16" t="n">
-        <v>1088</v>
+      <c r="C17" s="11" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1491,47 +1851,47 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>153</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>1144</v>
+      <c r="C19" s="11" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="21" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B21" s="14" t="s">
+      <c r="C20" s="11" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="21" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>10323</v>
+      <c r="C21" s="11" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
       <c r="B22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="16" t="n">
-        <v>2902</v>
+      <c r="C22" s="11" t="n">
+        <v>973</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>4128</v>
+      <c r="C23" s="11" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1539,15 +1899,15 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>485</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="16" t="n">
-        <v>1602</v>
+      <c r="C25" s="11" t="n">
+        <v>392</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1555,7 +1915,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>382</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1563,15 +1923,15 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="28" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B28" s="14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="28" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="12" t="n">
-        <v>5609</v>
+      <c r="C28" s="16" t="n">
+        <v>2998</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1579,15 +1939,15 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="30" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B30" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="30" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B30" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>160</v>
+      <c r="C30" s="12" t="n">
+        <v>34971</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1595,23 +1955,23 @@
         <v>30</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>1058</v>
+        <v>4591</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>293</v>
+      <c r="C32" s="16" t="n">
+        <v>7374</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>277</v>
+      <c r="C33" s="16" t="n">
+        <v>1767</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1619,7 +1979,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>1281</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1627,15 +1987,15 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>306</v>
+      <c r="C36" s="16" t="n">
+        <v>7033</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1643,23 +2003,23 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>533</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>271</v>
+      <c r="C38" s="16" t="n">
+        <v>1708</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>220</v>
+      <c r="C39" s="16" t="n">
+        <v>1522</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1667,47 +2027,47 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>484</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>196</v>
+      <c r="C41" s="16" t="n">
+        <v>1227</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B43" s="14" t="s">
+      <c r="C42" s="16" t="n">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="43" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="12" t="n">
-        <v>11510</v>
+      <c r="C43" s="16" t="n">
+        <v>1287</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="45" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B45" s="15" t="s">
+      <c r="C44" s="16" t="n">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="45" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B45" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>389</v>
+      <c r="C45" s="12" t="n">
+        <v>10950</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1715,7 +2075,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>551</v>
+        <v>468</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1723,31 +2083,31 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>852</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="16" t="n">
-        <v>3975</v>
+      <c r="C48" s="11" t="n">
+        <v>872</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
       <c r="B49" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="16" t="n">
-        <v>1138</v>
+      <c r="C49" s="11" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
       <c r="B50" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="16" t="n">
-        <v>1025</v>
+      <c r="C50" s="11" t="n">
+        <v>674</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1755,7 +2115,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>422</v>
+        <v>564</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1763,7 +2123,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>245</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1771,15 +2131,15 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>768</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="16" t="n">
-        <v>1274</v>
+      <c r="C54" s="11" t="n">
+        <v>925</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -1787,7 +2147,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>472</v>
+        <v>612</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1795,71 +2155,71 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B57" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="12" t="n">
-        <v>345712</v>
-      </c>
-    </row>
-    <row r="58" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B58" s="14" t="s">
+      <c r="C57" s="11" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="58" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="12" t="n">
-        <v>97916</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C58" s="11" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="16" t="n">
-        <v>17800</v>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C59" s="11" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="60" ht="11" customHeight="true" outlineLevel="3">
       <c r="B60" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="16" t="n">
-        <v>3240</v>
+      <c r="C60" s="11" t="n">
+        <v>285</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="16" t="n">
-        <v>7119</v>
+      <c r="C61" s="11" t="n">
+        <v>499</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>2340</v>
+      <c r="C62" s="11" t="n">
+        <v>702</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="16" t="n">
-        <v>3450</v>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C63" s="11" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="16" t="n">
-        <v>5040</v>
+      <c r="C64" s="11" t="n">
+        <v>197</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -1867,55 +2227,55 @@
         <v>64</v>
       </c>
       <c r="C65" s="16" t="n">
-        <v>9529</v>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="true" outlineLevel="3">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>3030</v>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B67" s="15" t="s">
+      <c r="C66" s="11" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B67" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="16" t="n">
-        <v>14810</v>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C67" s="12" t="n">
+        <v>30461</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="16" t="n">
-        <v>4650</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C68" s="11" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="16" t="n">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C69" s="11" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
       <c r="C70" s="16" t="n">
-        <v>2700</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>12816</v>
+      <c r="C71" s="11" t="n">
+        <v>860</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -1923,15 +2283,15 @@
         <v>71</v>
       </c>
       <c r="C72" s="16" t="n">
-        <v>9382</v>
-      </c>
-    </row>
-    <row r="73" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B73" s="14" t="s">
+        <v>5335</v>
+      </c>
+    </row>
+    <row r="73" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="12" t="n">
-        <v>5864</v>
+      <c r="C73" s="11" t="n">
+        <v>990</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -1939,15 +2299,15 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>451</v>
+        <v>885</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>8</v>
+      <c r="C75" s="16" t="n">
+        <v>3414</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -1955,7 +2315,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>743</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -1963,15 +2323,15 @@
         <v>76</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>1630</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="11" t="n">
-        <v>34</v>
+      <c r="C78" s="16" t="n">
+        <v>10696</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -1979,15 +2339,15 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>534</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="16" t="n">
-        <v>1823</v>
+      <c r="C80" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -1995,7 +2355,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>70</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
@@ -2003,15 +2363,15 @@
         <v>81</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B83" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B83" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>227</v>
+      <c r="C83" s="12" t="n">
+        <v>368946</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="2">
@@ -2019,39 +2379,39 @@
         <v>83</v>
       </c>
       <c r="C84" s="12" t="n">
-        <v>19888</v>
-      </c>
-    </row>
-    <row r="85" ht="11" customHeight="true" outlineLevel="3">
+        <v>130233</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C85" s="16" t="n">
+        <v>6589</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="11" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="87" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C86" s="16" t="n">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>519</v>
+      <c r="C87" s="16" t="n">
+        <v>1830</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>21</v>
+      <c r="C88" s="16" t="n">
+        <v>14000</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2059,15 +2419,15 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>174</v>
+        <v>330</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>523</v>
+      <c r="C90" s="16" t="n">
+        <v>2490</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2075,119 +2435,119 @@
         <v>90</v>
       </c>
       <c r="C91" s="16" t="n">
-        <v>3762</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="3">
+        <v>18045</v>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="16" t="n">
-        <v>4296</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C92" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
       <c r="C93" s="16" t="n">
-        <v>2473</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="11" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C94" s="16" t="n">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C95" s="16" t="n">
+        <v>9289</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="97" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C96" s="16" t="n">
+        <v>8495</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="98" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C97" s="16" t="n">
+        <v>9919</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C98" s="16" t="n">
+        <v>17325</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C99" s="16" t="n">
+        <v>5955</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C100" s="16" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C101" s="16" t="n">
+        <v>13746</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C102" s="16" t="n">
+        <v>9110</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="16" t="n">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B104" s="15" t="s">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B104" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>156</v>
+      <c r="C104" s="12" t="n">
+        <v>7682</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>38</v>
+      <c r="C105" s="16" t="n">
+        <v>1013</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
@@ -2195,7 +2555,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2203,7 +2563,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>453</v>
+        <v>572</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2211,7 +2571,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>76</v>
+        <v>931</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2219,7 +2579,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="16" t="n">
-        <v>3265</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
@@ -2227,7 +2587,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
@@ -2235,7 +2595,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>311</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2243,15 +2603,15 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="113" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B113" s="14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="113" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="12" t="n">
-        <v>31457</v>
+      <c r="C113" s="11" t="n">
+        <v>486</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2259,7 +2619,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>27</v>
+        <v>493</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2267,7 +2627,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>120</v>
+        <v>208</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2275,7 +2635,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>393</v>
+        <v>559</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2283,23 +2643,23 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="118" ht="11" customHeight="true" outlineLevel="3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="119" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B119" s="15" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="119" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B119" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="11" t="n">
-        <v>283</v>
+      <c r="C119" s="12" t="n">
+        <v>26115</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2307,7 +2667,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>131</v>
+        <v>670</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2315,7 +2675,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>60</v>
+        <v>415</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2323,7 +2683,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2331,7 +2691,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>171</v>
+        <v>333</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2339,31 +2699,31 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>736</v>
+        <v>321</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>602</v>
+      <c r="C125" s="16" t="n">
+        <v>3681</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="11" t="n">
-        <v>88</v>
+      <c r="C126" s="16" t="n">
+        <v>1700</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>602</v>
+      <c r="C127" s="16" t="n">
+        <v>2898</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2371,7 +2731,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="16" t="n">
-        <v>1152</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2379,7 +2739,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="16" t="n">
-        <v>1844</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2387,7 +2747,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>523</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2395,7 +2755,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>220</v>
+        <v>175</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2403,7 +2763,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>687</v>
+        <v>71</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2411,7 +2771,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>523</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2419,7 +2779,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>220</v>
+        <v>142</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2427,15 +2787,15 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>663</v>
+        <v>190</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="11" t="n">
-        <v>182</v>
+      <c r="C136" s="16" t="n">
+        <v>1017</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2443,7 +2803,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>499</v>
+        <v>840</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2451,15 +2811,15 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>563</v>
+        <v>817</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="11" t="n">
-        <v>273</v>
+      <c r="C139" s="16" t="n">
+        <v>1109</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2467,7 +2827,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>110</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2475,15 +2835,15 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>173</v>
+        <v>446</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="11" t="n">
-        <v>182</v>
+      <c r="C142" s="16" t="n">
+        <v>1770</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2491,7 +2851,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>29</v>
+        <v>208</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2499,7 +2859,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>602</v>
+        <v>182</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2507,7 +2867,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>88</v>
+        <v>269</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2515,15 +2875,15 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>21</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="16" t="n">
-        <v>1212</v>
+      <c r="C147" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2531,7 +2891,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="16" t="n">
-        <v>1232</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2539,7 +2899,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>182</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2547,7 +2907,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2555,23 +2915,23 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="152" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B152" s="15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B152" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>614</v>
+      <c r="C152" s="12" t="n">
+        <v>84849</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
       <c r="B153" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="11" t="n">
-        <v>22</v>
+      <c r="C153" s="16" t="n">
+        <v>1624</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2579,7 +2939,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>166</v>
+        <v>513</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2587,15 +2947,15 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>182</v>
+        <v>316</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
       <c r="B156" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C156" s="16" t="n">
-        <v>1177</v>
+      <c r="C156" s="11" t="n">
+        <v>584</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2603,7 +2963,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>602</v>
+        <v>257</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2611,7 +2971,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>22</v>
+        <v>581</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2619,7 +2979,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>792</v>
+        <v>60</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2627,7 +2987,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>273</v>
+        <v>538</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2635,7 +2995,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>138</v>
+        <v>556</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2643,23 +3003,23 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>182</v>
+        <v>533</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="11" t="n">
-        <v>62</v>
+      <c r="C163" s="16" t="n">
+        <v>2725</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="16" t="n">
-        <v>1782</v>
+      <c r="C164" s="11" t="n">
+        <v>517</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2667,7 +3027,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>602</v>
+        <v>257</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2675,15 +3035,15 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="11" t="n">
-        <v>197</v>
+      <c r="C167" s="16" t="n">
+        <v>2173</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2691,15 +3051,15 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>273</v>
+        <v>331</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="16" t="n">
-        <v>1944</v>
+      <c r="C169" s="11" t="n">
+        <v>882</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2707,7 +3067,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>602</v>
+        <v>258</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2715,7 +3075,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="16" t="n">
-        <v>2198</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2723,31 +3083,31 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>182</v>
+        <v>447</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
       <c r="B173" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C173" s="16" t="n">
-        <v>1310</v>
+      <c r="C173" s="11" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="11" t="n">
-        <v>523</v>
+      <c r="C174" s="16" t="n">
+        <v>4421</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="16" t="n">
-        <v>1249</v>
+      <c r="C175" s="11" t="n">
+        <v>184</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2755,15 +3115,15 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="11" t="n">
-        <v>306</v>
+      <c r="C177" s="16" t="n">
+        <v>2980</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2771,7 +3131,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>120</v>
+        <v>204</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2786,8 +3146,8 @@
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="11" t="n">
-        <v>104</v>
+      <c r="C180" s="16" t="n">
+        <v>2410</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2795,15 +3155,15 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="182" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B182" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="182" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="12" t="n">
-        <v>17161</v>
+      <c r="C182" s="11" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2811,7 +3171,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>1</v>
+        <v>744</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2819,15 +3179,15 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>580</v>
+        <v>63</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="11" t="n">
-        <v>86</v>
+      <c r="C185" s="16" t="n">
+        <v>3256</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2835,7 +3195,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>796</v>
+        <v>944</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -2843,7 +3203,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>174</v>
+        <v>371</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2851,15 +3211,15 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>179</v>
+        <v>543</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="16" t="n">
-        <v>1553</v>
+      <c r="C189" s="11" t="n">
+        <v>551</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2867,7 +3227,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>11</v>
+        <v>942</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2875,7 +3235,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>140</v>
+        <v>201</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2883,7 +3243,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>31</v>
+        <v>476</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2891,15 +3251,15 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>515</v>
+        <v>90</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="11" t="n">
-        <v>89</v>
+      <c r="C194" s="16" t="n">
+        <v>1534</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2907,23 +3267,23 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="196" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>302</v>
+        <v>286</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="11" t="n">
-        <v>742</v>
+      <c r="C197" s="16" t="n">
+        <v>2734</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -2931,23 +3291,23 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="199" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" ht="22" customHeight="true" outlineLevel="3">
       <c r="B199" s="15" t="s">
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>426</v>
+        <v>113</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="11" t="n">
-        <v>86</v>
+      <c r="C200" s="16" t="n">
+        <v>2541</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2955,7 +3315,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>450</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -2963,7 +3323,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>224</v>
+        <v>150</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2971,15 +3331,15 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>311</v>
+        <v>267</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="11" t="n">
-        <v>482</v>
+      <c r="C204" s="16" t="n">
+        <v>1667</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -2987,31 +3347,31 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>766</v>
+        <v>287</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
       <c r="B206" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="16" t="n">
-        <v>1047</v>
+      <c r="C206" s="11" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="11" t="n">
-        <v>657</v>
+      <c r="C207" s="16" t="n">
+        <v>2560</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
       <c r="B208" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C208" s="16" t="n">
-        <v>1014</v>
+      <c r="C208" s="11" t="n">
+        <v>304</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3019,15 +3379,15 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>238</v>
+        <v>311</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="11" t="n">
-        <v>108</v>
+      <c r="C210" s="16" t="n">
+        <v>4478</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3035,7 +3395,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>556</v>
+        <v>626</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3043,7 +3403,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3051,15 +3411,15 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>548</v>
+        <v>223</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
       <c r="B214" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="11" t="n">
-        <v>685</v>
+      <c r="C214" s="16" t="n">
+        <v>2447</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3067,7 +3427,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>654</v>
+        <v>525</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3075,7 +3435,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>696</v>
+        <v>844</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3083,23 +3443,23 @@
         <v>216</v>
       </c>
       <c r="C217" s="16" t="n">
-        <v>1389</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="11" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="219" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B219" s="14" t="s">
+      <c r="C218" s="16" t="n">
+        <v>3718</v>
+      </c>
+    </row>
+    <row r="219" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="12" t="n">
-        <v>4393</v>
+      <c r="C219" s="11" t="n">
+        <v>592</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3107,7 +3467,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>693</v>
+        <v>60</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3115,7 +3475,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>193</v>
+        <v>310</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3123,15 +3483,15 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>815</v>
+        <v>111</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="11" t="n">
-        <v>64</v>
+      <c r="C223" s="16" t="n">
+        <v>2744</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3139,7 +3499,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>149</v>
+        <v>220</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3147,15 +3507,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>376</v>
+        <v>666</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>3</v>
+      <c r="C226" s="16" t="n">
+        <v>2757</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3163,7 +3523,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>96</v>
+        <v>907</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3171,15 +3531,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>830</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>143</v>
+      <c r="C229" s="16" t="n">
+        <v>2564</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3187,7 +3547,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>59</v>
+        <v>248</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3195,23 +3555,23 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>299</v>
+        <v>385</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>47</v>
+      <c r="C232" s="16" t="n">
+        <v>2766</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="11" t="n">
-        <v>163</v>
+      <c r="C233" s="16" t="n">
+        <v>1920</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3219,7 +3579,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>123</v>
+        <v>219</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3227,39 +3587,39 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>251</v>
+        <v>94</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="237" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B237" s="14" t="s">
+      <c r="C236" s="16" t="n">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="237" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B237" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="12" t="n">
-        <v>21201</v>
-      </c>
-    </row>
-    <row r="238" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C237" s="11" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>28</v>
+        <v>371</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>80</v>
+      <c r="C239" s="16" t="n">
+        <v>1027</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3267,7 +3627,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>87</v>
+        <v>162</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3275,23 +3635,23 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>108</v>
+        <v>502</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="16" t="n">
-        <v>1192</v>
+      <c r="C242" s="11" t="n">
+        <v>263</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="16" t="n">
-        <v>1631</v>
+      <c r="C243" s="11" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3299,79 +3659,79 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="245" ht="22" customHeight="true" outlineLevel="3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="245" ht="11" customHeight="true" outlineLevel="3">
       <c r="B245" s="15" t="s">
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="246" ht="22" customHeight="true" outlineLevel="3">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="246" ht="11" customHeight="true" outlineLevel="3">
       <c r="B246" s="15" t="s">
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="247" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B247" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="247" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B247" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="11" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="248" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C247" s="12" t="n">
+        <v>28773</v>
+      </c>
+    </row>
+    <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="249" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C248" s="16" t="n">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="250" ht="22" customHeight="true" outlineLevel="3">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="11" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="251" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C250" s="16" t="n">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="252" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="true" outlineLevel="3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="11" t="n">
-        <v>10</v>
+      <c r="C253" s="16" t="n">
+        <v>2698</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3379,7 +3739,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>220</v>
+        <v>40</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3387,7 +3747,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>352</v>
+        <v>216</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3395,7 +3755,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>21</v>
+        <v>246</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3403,7 +3763,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>147</v>
+        <v>746</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3411,15 +3771,15 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>93</v>
+        <v>511</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="16" t="n">
-        <v>2534</v>
+      <c r="C259" s="11" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3427,31 +3787,31 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>626</v>
+        <v>161</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="16" t="n">
-        <v>1819</v>
+      <c r="C261" s="11" t="n">
+        <v>632</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="11" t="n">
-        <v>109</v>
+      <c r="C262" s="16" t="n">
+        <v>1457</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
       <c r="B263" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="16" t="n">
-        <v>1000</v>
+      <c r="C263" s="11" t="n">
+        <v>709</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3459,7 +3819,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>21</v>
+        <v>344</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3467,23 +3827,23 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>32</v>
+        <v>652</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
       <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="16" t="n">
-        <v>2640</v>
+      <c r="C266" s="11" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="16" t="n">
-        <v>3123</v>
+      <c r="C267" s="11" t="n">
+        <v>557</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3491,39 +3851,39 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>425</v>
+        <v>636</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="C269" s="16" t="n">
-        <v>2694</v>
-      </c>
-    </row>
-    <row r="270" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C269" s="11" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="271" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C270" s="16" t="n">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>2</v>
+      <c r="C271" s="16" t="n">
+        <v>2379</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>225</v>
+      <c r="C272" s="16" t="n">
+        <v>2257</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3531,15 +3891,15 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="274" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B274" s="14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="274" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B274" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="12" t="n">
-        <v>20958</v>
+      <c r="C274" s="11" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3547,7 +3907,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>557</v>
+        <v>412</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3555,31 +3915,31 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>937</v>
+        <v>925</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="16" t="n">
-        <v>3492</v>
+      <c r="C277" s="11" t="n">
+        <v>462</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="11" t="n">
-        <v>198</v>
+      <c r="C278" s="16" t="n">
+        <v>2015</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="11" t="n">
-        <v>318</v>
+      <c r="C279" s="16" t="n">
+        <v>1877</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3587,15 +3947,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>319</v>
+        <v>24</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="11" t="n">
-        <v>374</v>
+      <c r="C281" s="16" t="n">
+        <v>2636</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3603,15 +3963,15 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="283" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B283" s="15" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="283" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B283" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="11" t="n">
-        <v>577</v>
+      <c r="C283" s="12" t="n">
+        <v>4608</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3619,7 +3979,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>937</v>
+        <v>880</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3627,7 +3987,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>414</v>
+        <v>128</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3635,7 +3995,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>778</v>
+        <v>506</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3643,7 +4003,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>505</v>
+        <v>318</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -3651,7 +4011,7 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>2</v>
+        <v>361</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3659,7 +4019,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3667,7 +4027,7 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3675,7 +4035,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>13</v>
+        <v>352</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3683,7 +4043,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>21</v>
+        <v>209</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3691,15 +4051,15 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>41</v>
+        <v>238</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="16" t="n">
-        <v>7448</v>
+      <c r="C294" s="11" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -3707,15 +4067,15 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>6</v>
+        <v>272</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="16" t="n">
-        <v>2229</v>
+      <c r="C296" s="11" t="n">
+        <v>508</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -3723,7 +4083,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>665</v>
+        <v>424</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -3731,15 +4091,15 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="299" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B299" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="17" t="n">
-        <v>200</v>
+      <c r="C299" s="11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -3747,15 +4107,15 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B301" s="15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B301" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="11" t="n">
-        <v>31</v>
+      <c r="C301" s="12" t="n">
+        <v>21329</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3763,7 +4123,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>12</v>
+        <v>232</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -3771,15 +4131,15 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="304" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B304" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="12" t="n">
-        <v>126674</v>
+      <c r="C304" s="11" t="n">
+        <v>284</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -3787,7 +4147,7 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -3795,47 +4155,47 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="307" ht="22" customHeight="true" outlineLevel="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="307" ht="11" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="308" ht="22" customHeight="true" outlineLevel="3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="C308" s="16" t="n">
-        <v>3465</v>
-      </c>
-    </row>
-    <row r="309" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C308" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="310" ht="22" customHeight="true" outlineLevel="3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="16" t="n">
-        <v>3953</v>
-      </c>
-    </row>
-    <row r="311" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C310" s="11" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>440</v>
+        <v>46</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -3843,23 +4203,23 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="313" ht="11" customHeight="true" outlineLevel="3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="313" ht="22" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>362</v>
+        <v>150</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="16" t="n">
-        <v>3967</v>
+      <c r="C314" s="11" t="n">
+        <v>247</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -3867,7 +4227,7 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>763</v>
+        <v>238</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -3875,7 +4235,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>2</v>
+        <v>438</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -3883,23 +4243,23 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="318" ht="22" customHeight="true" outlineLevel="3">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="319" ht="22" customHeight="true" outlineLevel="3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>182</v>
+        <v>30</v>
       </c>
     </row>
     <row r="320" ht="22" customHeight="true" outlineLevel="3">
@@ -3907,15 +4267,15 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>848</v>
+        <v>236</v>
       </c>
     </row>
     <row r="321" ht="22" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="16" t="n">
-        <v>10935</v>
+      <c r="C321" s="11" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="322" ht="22" customHeight="true" outlineLevel="3">
@@ -3923,7 +4283,7 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>563</v>
+        <v>19</v>
       </c>
     </row>
     <row r="323" ht="22" customHeight="true" outlineLevel="3">
@@ -3931,15 +4291,15 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>860</v>
+        <v>259</v>
       </c>
     </row>
     <row r="324" ht="22" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="16" t="n">
-        <v>1011</v>
+      <c r="C324" s="11" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="325" ht="22" customHeight="true" outlineLevel="3">
@@ -3947,15 +4307,15 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>515</v>
+        <v>283</v>
       </c>
     </row>
     <row r="326" ht="22" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="16" t="n">
-        <v>9948</v>
+      <c r="C326" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="327" ht="22" customHeight="true" outlineLevel="3">
@@ -3963,7 +4323,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>168</v>
+        <v>72</v>
       </c>
     </row>
     <row r="328" ht="22" customHeight="true" outlineLevel="3">
@@ -3971,23 +4331,23 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>517</v>
+        <v>228</v>
       </c>
     </row>
     <row r="329" ht="22" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="16" t="n">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="330" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C329" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>309</v>
+        <v>153</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -3995,7 +4355,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>491</v>
+        <v>91</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4003,7 +4363,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -4011,7 +4371,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>519</v>
+        <v>288</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -4019,63 +4379,63 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>15</v>
+        <v>227</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="11" t="n">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="336" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C335" s="16" t="n">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="336" ht="22" customHeight="true" outlineLevel="3">
       <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="337" ht="22" customHeight="true" outlineLevel="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="11" t="n">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="338" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C337" s="16" t="n">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="339" ht="22" customHeight="true" outlineLevel="3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="340" ht="22" customHeight="true" outlineLevel="3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
       <c r="C340" s="16" t="n">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="341" ht="22" customHeight="true" outlineLevel="3">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>717</v>
+        <v>20</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4083,23 +4443,23 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="343" ht="22" customHeight="true" outlineLevel="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="11" t="n">
-        <v>720</v>
+      <c r="C343" s="16" t="n">
+        <v>1447</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="11" t="n">
-        <v>74</v>
+      <c r="C344" s="16" t="n">
+        <v>4394</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4107,7 +4467,7 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>15</v>
+        <v>818</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4115,71 +4475,71 @@
         <v>345</v>
       </c>
       <c r="C346" s="16" t="n">
-        <v>2224</v>
-      </c>
-    </row>
-    <row r="347" ht="22" customHeight="true" outlineLevel="3">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B348" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B348" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="11" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B349" s="15" t="s">
+      <c r="C348" s="17" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B349" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="C349" s="16" t="n">
-        <v>1638</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B350" s="15" t="s">
+      <c r="C349" s="17" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B350" s="19" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B351" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B351" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="16" t="n">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B352" s="15" t="s">
+      <c r="C351" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B352" s="19" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="16" t="n">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B353" s="15" t="s">
+      <c r="C352" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B353" s="19" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="354" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B354" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B354" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="16" t="n">
-        <v>1322</v>
+      <c r="C354" s="12" t="n">
+        <v>16210</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4187,47 +4547,47 @@
         <v>354</v>
       </c>
       <c r="C355" s="16" t="n">
-        <v>2447</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="357" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C356" s="16" t="n">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="3">
       <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="16" t="n">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="358" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C357" s="11" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="358" ht="22" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="16" t="n">
-        <v>1588</v>
+      <c r="C358" s="11" t="n">
+        <v>804</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="16" t="n">
-        <v>2046</v>
+      <c r="C359" s="11" t="n">
+        <v>992</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
       <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="16" t="n">
-        <v>4319</v>
+      <c r="C360" s="11" t="n">
+        <v>373</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
@@ -4235,15 +4595,15 @@
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>15</v>
+        <v>360</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
       <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="C362" s="16" t="n">
-        <v>1038</v>
+      <c r="C362" s="11" t="n">
+        <v>116</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4251,15 +4611,15 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>15</v>
+        <v>237</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
       <c r="B364" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="C364" s="16" t="n">
-        <v>1541</v>
+      <c r="C364" s="11" t="n">
+        <v>184</v>
       </c>
     </row>
     <row r="365" ht="11" customHeight="true" outlineLevel="3">
@@ -4267,39 +4627,983 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>849</v>
+        <v>211</v>
       </c>
     </row>
     <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="C366" s="16" t="n">
-        <v>17346</v>
-      </c>
-    </row>
-    <row r="367" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C366" s="11" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="C367" s="16" t="n">
-        <v>6776</v>
+      <c r="C367" s="11" t="n">
+        <v>785</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
       <c r="B368" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="C368" s="16" t="n">
-        <v>21242</v>
-      </c>
-    </row>
-    <row r="369" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C368" s="11" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="C369" s="16" t="n">
-        <v>7584</v>
+      <c r="C369" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="370" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B370" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C370" s="11" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B371" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="C371" s="11" t="n">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B372" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="C372" s="11" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B373" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="C373" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B374" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="C374" s="11" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B375" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="C375" s="11" t="n">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B376" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C376" s="11" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B377" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C377" s="11" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B378" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="C378" s="11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="379" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B379" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C379" s="11" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="380" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B380" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C380" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="381" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B381" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="C381" s="11" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="382" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B382" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C382" s="11" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B383" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C383" s="11" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="384" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B384" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C384" s="11" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B385" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C385" s="11" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B386" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="C386" s="11" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="387" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B387" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="C387" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B388" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="C388" s="16" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B389" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C389" s="16" t="n">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B390" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C390" s="11" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="391" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B391" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C391" s="11" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="392" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B392" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="C392" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="393" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B393" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="C393" s="11" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="394" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B394" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C394" s="11" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B395" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="C395" s="17" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="396" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B396" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="C396" s="11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B397" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="C397" s="11" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B398" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C398" s="11" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="399" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B399" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="C399" s="12" t="n">
+        <v>48820</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B400" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C400" s="11" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B401" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="C401" s="11" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B402" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C402" s="11" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B403" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C403" s="11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="404" ht="33" customHeight="true" outlineLevel="3">
+      <c r="B404" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="C404" s="11" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="405" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B405" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C405" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="406" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B406" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C406" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B407" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C407" s="11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B408" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="C408" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B409" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="11" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="410" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B410" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C410" s="11" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B411" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="16" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B412" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C412" s="11" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="413" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B413" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="11" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B414" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="16" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B415" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C415" s="11" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="416" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B416" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="C416" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="417" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B417" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="C417" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="418" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B418" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="C418" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="419" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B419" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="16" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B420" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C420" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="421" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B421" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C421" s="11" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="422" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B422" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="C422" s="11" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="423" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B423" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="C423" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="424" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B424" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C424" s="11" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="425" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B425" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="C425" s="11" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="426" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B426" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C426" s="16" t="n">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="427" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B427" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C427" s="11" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B428" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C428" s="11" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B429" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C429" s="11" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="430" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B430" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C430" s="11" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="431" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B431" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C431" s="11" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="432" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B432" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="C432" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="433" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B433" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C433" s="11" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="434" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B434" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C434" s="11" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="435" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B435" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C435" s="11" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="436" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B436" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="C436" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="437" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B437" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C437" s="11" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="438" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B438" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C438" s="11" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="439" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B439" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C439" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="440" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B440" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C440" s="11" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="441" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B441" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C441" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="442" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B442" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C442" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="443" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B443" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C443" s="11" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="444" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B444" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="C444" s="11" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="445" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B445" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C445" s="11" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="446" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B446" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C446" s="11" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="447" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B447" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="C447" s="11" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="448" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B448" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="C448" s="11" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="449" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B449" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C449" s="11" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="450" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B450" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="C450" s="11" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="451" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B451" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="C451" s="11" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="452" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B452" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="C452" s="11" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="453" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B453" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="C453" s="11" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="454" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B454" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C454" s="11" t="n">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="455" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B455" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="C455" s="11" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="456" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B456" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="C456" s="11" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="457" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B457" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="C457" s="11" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B458" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C458" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="459" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B459" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="C459" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="460" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B460" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C460" s="16" t="n">
+        <v>6338</v>
+      </c>
+    </row>
+    <row r="461" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B461" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="C461" s="11" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="462" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B462" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C462" s="11" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="463" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B463" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="C463" s="16" t="n">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="464" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B464" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C464" s="11" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="465" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B465" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="C465" s="11" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="466" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B466" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="C466" s="16" t="n">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="467" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B467" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C467" s="11" t="n">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="468" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B468" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C468" s="11" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="469" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B469" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C469" s="16" t="n">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="470" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B470" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="C470" s="16" t="n">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="471" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B471" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="C471" s="11" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="472" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B472" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C472" s="16" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="473" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B473" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="C473" s="11" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="474" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B474" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C474" s="11" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="475" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B475" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="C475" s="16" t="n">
+        <v>3304</v>
+      </c>
+    </row>
+    <row r="476" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B476" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="C476" s="16" t="n">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="477" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B477" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="C477" s="11" t="n">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="478" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B478" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="C478" s="11" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="479" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B479" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="C479" s="11" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="480" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B480" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="C480" s="12" t="n">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="481" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B481" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="C481" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="482" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B482" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="C482" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="483" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B483" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="C483" s="11" t="n">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="484" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B484" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="C484" s="16" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="485" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B485" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="C485" s="16" t="n">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="486" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B486" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="C486" s="11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="487" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B487" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="C487" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/client/dist/Sorce/balanceKR.xlsx
+++ b/client/dist/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.12.2025 16:15:15</t>
+    <t>Период: на 23.02.2026 11:15:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,19 +62,19 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Lacmi Гарячий шоколад УБ 20г /90шт</t>
+  </si>
+  <si>
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
+    <t>Желе апельсин УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт</t>
@@ -83,30 +83,18 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Какао-порошок 22% УБ 60г /26шт</t>
+    <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
-    <t>Какао-порошок УБ 80г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -116,42 +104,45 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Ванільний цукор УБ 35г /36шт</t>
+  </si>
+  <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желатин УБ 25г /42шт</t>
   </si>
   <si>
-    <t>Желатин УБ 25г /42шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
@@ -170,18 +161,24 @@
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
-    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
+    <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
+    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
@@ -197,12 +194,15 @@
     <t>Суміш зелені УБ 10г /24шт</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
+    <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
+    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
@@ -215,9 +215,6 @@
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -251,12 +248,12 @@
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -272,21 +269,18 @@
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -299,18 +293,21 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -347,9 +344,6 @@
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
-    <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>РУЛЕТ П'янка вишня ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -383,9 +377,6 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -395,42 +386,45 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ</t>
+    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
@@ -443,6 +437,9 @@
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -452,12 +449,12 @@
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers лимон ВКФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers молоко ВКФ 216г /16шт</t>
-  </si>
-  <si>
     <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -512,13 +509,7 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
@@ -527,91 +518,64 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
@@ -620,42 +584,30 @@
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
@@ -665,78 +617,51 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Slices ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
@@ -752,12 +677,6 @@
     <t>Рошен евкаліпт-ментол РЦ 200г /12шт</t>
   </si>
   <si>
-    <t>Шалена бджілка ВКФ 200г /12шт</t>
-  </si>
-  <si>
-    <t>Шалена бджілка РЦ 200г /12шт</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
   </si>
   <si>
@@ -779,9 +698,6 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -794,9 +710,6 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -857,6 +770,9 @@
     <t>Рошен джус мікс РЦ 1кг /8пак /</t>
   </si>
   <si>
+    <t>Рошен евкаліпт-ментол КрКФ 1кг /8пак /</t>
+  </si>
+  <si>
     <t>Цитрусовий мікс РЦ 1кг /7пак /</t>
   </si>
   <si>
@@ -875,45 +791,45 @@
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Assortment Elegant 145г/8</t>
-  </si>
-  <si>
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Chocolateria ВКФ 256г /8шт</t>
-  </si>
-  <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
+    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters віски-лікер ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Shooters з бренді-лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters з ромовим лікером ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
     <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -935,27 +851,15 @@
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
   </si>
   <si>
     <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
   </si>
   <si>
-    <t>Lovita Brownie з какао ККФ 152г /21шт</t>
-  </si>
-  <si>
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
@@ -974,18 +878,12 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -995,9 +893,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
@@ -1010,12 +905,6 @@
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт</t>
-  </si>
-  <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
@@ -1025,9 +914,6 @@
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -1040,12 +926,6 @@
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -1058,40 +938,22 @@
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ 2026</t>
-  </si>
-  <si>
-    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
-  </si>
-  <si>
-    <t>Н/п №6 26 Веселе свято РЦ 458г /4шт</t>
-  </si>
-  <si>
-    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
-  </si>
-  <si>
-    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
-    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Boo! Bear РЦ 1кг /5пак АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
-    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
@@ -1100,34 +962,31 @@
     <t>Flaksi какао ККФ 0.5кг /8пак</t>
   </si>
   <si>
+    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Ko-Ko Choco White 1кг/5</t>
-  </si>
-  <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
-    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+    <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
+  </si>
+  <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
   </si>
   <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
@@ -1136,9 +995,6 @@
     <t>Krock з арахісом ВКФ 1кг /8пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Milaxy ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1151,12 +1007,18 @@
     <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1166,19 +1028,31 @@
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
@@ -1190,21 +1064,15 @@
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
+    <t>Johnny Krocker choco ВКФ 350г /12шт PL</t>
+  </si>
+  <si>
     <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
   </si>
   <si>
@@ -1229,18 +1097,12 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1250,9 +1112,6 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1265,24 +1124,12 @@
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
@@ -1310,40 +1157,28 @@
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
@@ -1361,78 +1196,39 @@
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
-    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
@@ -1442,43 +1238,7 @@
     <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
   </si>
   <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>ФІГУРКИ</t>
-  </si>
-  <si>
-    <t>Кролик Roshen зимовий ВКФ 100г /12шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1705,12 +1465,6 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1730,7 +1484,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C487"/>
+  <dimension ref="C407"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1795,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>365</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1803,7 +1557,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>453025</v>
+        <v>379208</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1811,7 +1565,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>84079</v>
+        <v>102966</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1819,7 +1573,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>7697</v>
+        <v>9465</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1827,7 +1581,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>727</v>
+        <v>880</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1835,7 +1589,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>912</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1843,7 +1597,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>168</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1851,7 +1605,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>36</v>
+        <v>645</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1859,15 +1613,15 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>152</v>
+        <v>604</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>440</v>
+      <c r="C20" s="16" t="n">
+        <v>1146</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1875,7 +1629,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1883,7 +1637,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>973</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1891,7 +1645,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>56</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1899,31 +1653,31 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>103</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B26" s="15" t="s">
+      <c r="C25" s="16" t="n">
+        <v>3779</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B26" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>164</v>
+      <c r="C26" s="12" t="n">
+        <v>36647</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>242</v>
+      <c r="C27" s="16" t="n">
+        <v>1958</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1931,23 +1685,23 @@
         <v>27</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>2998</v>
+        <v>8052</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="30" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B30" s="14" t="s">
+      <c r="C29" s="16" t="n">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="30" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="12" t="n">
-        <v>34971</v>
+      <c r="C30" s="16" t="n">
+        <v>1767</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1955,15 +1709,15 @@
         <v>30</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>4591</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>7374</v>
+      <c r="C32" s="11" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1971,7 +1725,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>1767</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1979,7 +1733,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>5308</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1987,7 +1741,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>350</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1995,7 +1749,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>7033</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -2003,71 +1757,71 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>24</v>
+        <v>412</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="16" t="n">
-        <v>1708</v>
+      <c r="C38" s="11" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="16" t="n">
-        <v>1522</v>
+      <c r="C39" s="11" t="n">
+        <v>793</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>8</v>
+      <c r="C40" s="16" t="n">
+        <v>1049</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="16" t="n">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="42" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B42" s="15" t="s">
+      <c r="C41" s="11" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B42" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="16" t="n">
-        <v>1388</v>
+      <c r="C42" s="12" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="16" t="n">
-        <v>1287</v>
+      <c r="C43" s="11" t="n">
+        <v>613</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="16" t="n">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="45" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B45" s="14" t="s">
+      <c r="C44" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="12" t="n">
-        <v>10950</v>
+      <c r="C45" s="11" t="n">
+        <v>456</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -2075,7 +1829,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>468</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -2083,7 +1837,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>124</v>
+        <v>446</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -2091,7 +1845,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>872</v>
+        <v>777</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -2099,7 +1853,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>68</v>
+        <v>575</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2107,7 +1861,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>674</v>
+        <v>926</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -2115,7 +1869,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>564</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2123,7 +1877,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>65</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2131,7 +1885,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>247</v>
+        <v>305</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2139,15 +1893,15 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>925</v>
+        <v>503</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>612</v>
+      <c r="C55" s="16" t="n">
+        <v>1071</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2155,7 +1909,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2163,7 +1917,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>348</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2171,15 +1925,15 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>62</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>626</v>
+      <c r="C59" s="16" t="n">
+        <v>1047</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2187,15 +1941,15 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="61" ht="11" customHeight="true" outlineLevel="3">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>499</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2203,7 +1957,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>702</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2211,7 +1965,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>533</v>
+        <v>701</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2219,7 +1973,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>197</v>
+        <v>413</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2227,39 +1981,39 @@
         <v>64</v>
       </c>
       <c r="C65" s="16" t="n">
-        <v>2077</v>
-      </c>
-    </row>
-    <row r="66" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B66" s="15" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B66" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="67" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B67" s="14" t="s">
+      <c r="C66" s="12" t="n">
+        <v>44854</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="12" t="n">
-        <v>30461</v>
+      <c r="C67" s="11" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>563</v>
+      <c r="C68" s="16" t="n">
+        <v>2101</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>884</v>
+      <c r="C69" s="16" t="n">
+        <v>1695</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2267,31 +2021,31 @@
         <v>69</v>
       </c>
       <c r="C70" s="16" t="n">
-        <v>1591</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>860</v>
+      <c r="C71" s="16" t="n">
+        <v>9365</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="16" t="n">
-        <v>5335</v>
+      <c r="C72" s="11" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
       <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="11" t="n">
-        <v>990</v>
+      <c r="C73" s="16" t="n">
+        <v>3067</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2299,23 +2053,23 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>885</v>
+        <v>254</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="16" t="n">
-        <v>3414</v>
+      <c r="C75" s="11" t="n">
+        <v>416</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>234</v>
+      <c r="C76" s="16" t="n">
+        <v>3293</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -2323,7 +2077,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>4198</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2331,7 +2085,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>10696</v>
+        <v>21138</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2339,7 +2093,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>400</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2347,7 +2101,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2355,63 +2109,63 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B82" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B82" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B83" s="13" t="s">
+      <c r="C82" s="12" t="n">
+        <v>276242</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B83" s="14" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="12" t="n">
-        <v>368946</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B84" s="14" t="s">
+        <v>20670</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="12" t="n">
-        <v>130233</v>
+      <c r="C84" s="11" t="n">
+        <v>805</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="16" t="n">
-        <v>6589</v>
+      <c r="C85" s="11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="16" t="n">
-        <v>3708</v>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C86" s="11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C87" s="16" t="n">
-        <v>1830</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="16" t="n">
-        <v>14000</v>
+      <c r="C88" s="11" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2419,23 +2173,23 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="16" t="n">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C90" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="16" t="n">
-        <v>18045</v>
+      <c r="C91" s="11" t="n">
+        <v>459</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="true" outlineLevel="3">
@@ -2443,7 +2197,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="true" outlineLevel="3">
@@ -2451,15 +2205,15 @@
         <v>92</v>
       </c>
       <c r="C93" s="16" t="n">
-        <v>3200</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="16" t="n">
-        <v>1870</v>
+      <c r="C94" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="true" outlineLevel="3">
@@ -2467,47 +2221,47 @@
         <v>94</v>
       </c>
       <c r="C95" s="16" t="n">
-        <v>9289</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="16" t="n">
-        <v>8495</v>
+      <c r="C96" s="11" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="16" t="n">
-        <v>9919</v>
+      <c r="C97" s="11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>17325</v>
+      <c r="C98" s="11" t="n">
+        <v>844</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="16" t="n">
-        <v>5955</v>
+      <c r="C99" s="11" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="16" t="n">
-        <v>1300</v>
+      <c r="C100" s="11" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
@@ -2515,39 +2269,39 @@
         <v>100</v>
       </c>
       <c r="C101" s="16" t="n">
-        <v>13746</v>
+        <v>7178</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="16" t="n">
-        <v>9110</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B103" s="15" t="s">
+      <c r="C102" s="11" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B103" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="16" t="n">
-        <v>3022</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B104" s="14" t="s">
+      <c r="C103" s="12" t="n">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="12" t="n">
-        <v>7682</v>
+      <c r="C104" s="11" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="16" t="n">
-        <v>1013</v>
+      <c r="C105" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
@@ -2555,7 +2309,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>198</v>
+        <v>400</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2563,31 +2317,31 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>572</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>931</v>
+      <c r="C108" s="16" t="n">
+        <v>1238</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="16" t="n">
-        <v>1394</v>
+      <c r="C109" s="11" t="n">
+        <v>505</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>34</v>
+      <c r="C110" s="16" t="n">
+        <v>1081</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
@@ -2595,7 +2349,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>398</v>
+        <v>49</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2603,7 +2357,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>501</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2611,7 +2365,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>486</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2619,7 +2373,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>493</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2627,39 +2381,39 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="116" ht="11" customHeight="true" outlineLevel="3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="true" outlineLevel="3">
       <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="117" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B117" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B117" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="11" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="118" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C117" s="12" t="n">
+        <v>66209</v>
+      </c>
+    </row>
+    <row r="118" ht="11" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="119" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B119" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="12" t="n">
-        <v>26115</v>
+      <c r="C119" s="11" t="n">
+        <v>760</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2667,7 +2421,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>670</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2675,31 +2429,31 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>415</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="11" t="n">
-        <v>26</v>
+      <c r="C122" s="16" t="n">
+        <v>28380</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>333</v>
+      <c r="C123" s="16" t="n">
+        <v>10171</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
       <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>321</v>
+      <c r="C124" s="16" t="n">
+        <v>5750</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2707,15 +2461,15 @@
         <v>124</v>
       </c>
       <c r="C125" s="16" t="n">
-        <v>3681</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="16" t="n">
-        <v>1700</v>
+      <c r="C126" s="11" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2723,23 +2477,23 @@
         <v>126</v>
       </c>
       <c r="C127" s="16" t="n">
-        <v>2898</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="16" t="n">
-        <v>3400</v>
+      <c r="C128" s="11" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
       <c r="B129" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="16" t="n">
-        <v>3224</v>
+      <c r="C129" s="11" t="n">
+        <v>244</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2747,7 +2501,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2755,7 +2509,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>175</v>
+        <v>377</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2763,15 +2517,15 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>71</v>
+        <v>680</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>26</v>
+      <c r="C133" s="16" t="n">
+        <v>1974</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2779,31 +2533,31 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="135" ht="11" customHeight="true" outlineLevel="3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>190</v>
+      <c r="C135" s="16" t="n">
+        <v>1879</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="16" t="n">
-        <v>1017</v>
+      <c r="C136" s="11" t="n">
+        <v>184</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="11" t="n">
-        <v>840</v>
+      <c r="C137" s="16" t="n">
+        <v>1357</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2811,15 +2565,15 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>817</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="16" t="n">
-        <v>1109</v>
+      <c r="C139" s="11" t="n">
+        <v>229</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2827,7 +2581,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2835,15 +2589,15 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>446</v>
+        <v>835</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="16" t="n">
-        <v>1770</v>
+      <c r="C142" s="11" t="n">
+        <v>149</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2851,7 +2605,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>208</v>
+        <v>83</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2859,7 +2613,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>182</v>
+        <v>262</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2867,7 +2621,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2875,31 +2629,31 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>340</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="11" t="n">
-        <v>1</v>
+      <c r="C147" s="16" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
       <c r="B148" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="16" t="n">
-        <v>1542</v>
+      <c r="C148" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="11" t="n">
-        <v>28</v>
+      <c r="C149" s="16" t="n">
+        <v>1207</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2907,31 +2661,31 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="151" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B151" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="151" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B151" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C151" s="11" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="152" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B152" s="14" t="s">
+      <c r="C151" s="12" t="n">
+        <v>79137</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B152" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="12" t="n">
-        <v>84849</v>
+      <c r="C152" s="11" t="n">
+        <v>512</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
       <c r="B153" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="16" t="n">
-        <v>1624</v>
+      <c r="C153" s="11" t="n">
+        <v>519</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2939,7 +2693,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>513</v>
+        <v>130</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2947,7 +2701,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>316</v>
+        <v>223</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2955,7 +2709,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>584</v>
+        <v>111</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2963,7 +2717,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>257</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2971,7 +2725,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>581</v>
+        <v>143</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2979,7 +2733,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>60</v>
+        <v>172</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2987,7 +2741,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>538</v>
+        <v>108</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2995,23 +2749,23 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>556</v>
+        <v>435</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="11" t="n">
-        <v>533</v>
+      <c r="C162" s="16" t="n">
+        <v>3633</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="16" t="n">
-        <v>2725</v>
+      <c r="C163" s="11" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -3019,7 +2773,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>517</v>
+        <v>887</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -3027,7 +2781,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>257</v>
+        <v>470</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -3035,23 +2789,23 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>92</v>
+        <v>698</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="16" t="n">
-        <v>2173</v>
+      <c r="C167" s="11" t="n">
+        <v>642</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
       <c r="B168" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="11" t="n">
-        <v>331</v>
+      <c r="C168" s="16" t="n">
+        <v>3440</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -3059,7 +2813,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>882</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -3067,15 +2821,15 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>258</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="16" t="n">
-        <v>1361</v>
+      <c r="C171" s="11" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -3083,7 +2837,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>447</v>
+        <v>74</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -3091,15 +2845,15 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>133</v>
+        <v>211</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="16" t="n">
-        <v>4421</v>
+      <c r="C174" s="11" t="n">
+        <v>693</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -3107,7 +2861,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>184</v>
+        <v>298</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -3115,7 +2869,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>78</v>
+        <v>363</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -3123,15 +2877,15 @@
         <v>176</v>
       </c>
       <c r="C177" s="16" t="n">
-        <v>2980</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="11" t="n">
-        <v>204</v>
+      <c r="C178" s="16" t="n">
+        <v>2723</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3139,47 +2893,47 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="16" t="n">
-        <v>2410</v>
-      </c>
-    </row>
-    <row r="181" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C180" s="11" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="181" ht="22" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="11" t="n">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="182" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C181" s="16" t="n">
+        <v>13669</v>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="183" ht="11" customHeight="true" outlineLevel="3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="11" t="n">
-        <v>744</v>
+      <c r="C183" s="16" t="n">
+        <v>1690</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="11" t="n">
-        <v>63</v>
+      <c r="C184" s="16" t="n">
+        <v>14903</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3187,23 +2941,23 @@
         <v>184</v>
       </c>
       <c r="C185" s="16" t="n">
-        <v>3256</v>
-      </c>
-    </row>
-    <row r="186" ht="11" customHeight="true" outlineLevel="3">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="true" outlineLevel="3">
       <c r="B186" s="15" t="s">
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="187" ht="11" customHeight="true" outlineLevel="3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>371</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3211,23 +2965,23 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>543</v>
+        <v>260</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="190" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C189" s="16" t="n">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="true" outlineLevel="3">
       <c r="B190" s="15" t="s">
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>942</v>
+        <v>153</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3235,7 +2989,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>201</v>
+        <v>96</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3243,7 +2997,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>476</v>
+        <v>152</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -3251,15 +3005,15 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="16" t="n">
-        <v>1534</v>
+      <c r="C194" s="11" t="n">
+        <v>202</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3267,39 +3021,39 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="196" ht="22" customHeight="true" outlineLevel="3">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>286</v>
+        <v>321</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="16" t="n">
-        <v>2734</v>
+      <c r="C197" s="11" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="199" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C198" s="16" t="n">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="199" ht="11" customHeight="true" outlineLevel="3">
       <c r="B199" s="15" t="s">
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>113</v>
+        <v>299</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3307,7 +3061,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="16" t="n">
-        <v>2541</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3315,7 +3069,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>10</v>
+        <v>226</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3323,7 +3077,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>150</v>
+        <v>892</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3331,7 +3085,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>267</v>
+        <v>670</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3339,7 +3093,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="16" t="n">
-        <v>1667</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3347,7 +3101,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3355,7 +3109,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>85</v>
+        <v>225</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3363,7 +3117,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="16" t="n">
-        <v>2560</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3371,7 +3125,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>304</v>
+        <v>672</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3379,23 +3133,23 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>311</v>
+        <v>201</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="16" t="n">
-        <v>4478</v>
+      <c r="C210" s="11" t="n">
+        <v>340</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
       <c r="B211" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="11" t="n">
-        <v>626</v>
+      <c r="C211" s="16" t="n">
+        <v>2442</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3403,7 +3157,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3411,15 +3165,15 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>223</v>
+        <v>385</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
       <c r="B214" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="16" t="n">
-        <v>2447</v>
+      <c r="C214" s="11" t="n">
+        <v>329</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3427,7 +3181,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>525</v>
+        <v>78</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3435,23 +3189,23 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>844</v>
+        <v>292</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="16" t="n">
-        <v>1061</v>
+      <c r="C217" s="11" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="16" t="n">
-        <v>3718</v>
+      <c r="C218" s="11" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3459,15 +3213,15 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="220" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B220" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="220" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B220" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="11" t="n">
-        <v>60</v>
+      <c r="C220" s="12" t="n">
+        <v>40057</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3475,7 +3229,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>310</v>
+        <v>813</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3483,7 +3237,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3491,7 +3245,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="16" t="n">
-        <v>2744</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3499,7 +3253,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>220</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3507,7 +3261,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>666</v>
+        <v>979</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3515,7 +3269,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="16" t="n">
-        <v>2757</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3523,7 +3277,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>907</v>
+        <v>216</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3531,15 +3285,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>9</v>
+        <v>386</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="16" t="n">
-        <v>2564</v>
+      <c r="C229" s="11" t="n">
+        <v>410</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3547,7 +3301,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>248</v>
+        <v>325</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3555,7 +3309,7 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>385</v>
+        <v>302</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3563,7 +3317,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="16" t="n">
-        <v>2766</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3571,15 +3325,15 @@
         <v>232</v>
       </c>
       <c r="C233" s="16" t="n">
-        <v>1920</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
       <c r="B234" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="11" t="n">
-        <v>219</v>
+      <c r="C234" s="16" t="n">
+        <v>1332</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3587,7 +3341,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>94</v>
+        <v>781</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3595,7 +3349,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="16" t="n">
-        <v>3725</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3603,15 +3357,15 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>750</v>
+        <v>293</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="11" t="n">
-        <v>371</v>
+      <c r="C238" s="16" t="n">
+        <v>1250</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3619,7 +3373,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="16" t="n">
-        <v>1027</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3627,39 +3381,39 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>162</v>
+        <v>648</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="11" t="n">
-        <v>502</v>
+      <c r="C241" s="16" t="n">
+        <v>1336</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="11" t="n">
-        <v>263</v>
+      <c r="C242" s="16" t="n">
+        <v>1521</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="11" t="n">
-        <v>74</v>
+      <c r="C243" s="16" t="n">
+        <v>2946</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="11" t="n">
-        <v>166</v>
+      <c r="C244" s="16" t="n">
+        <v>1368</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3667,7 +3421,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>364</v>
+        <v>793</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3675,15 +3429,15 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="247" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B247" s="14" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="247" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="12" t="n">
-        <v>28773</v>
+      <c r="C247" s="11" t="n">
+        <v>621</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3691,15 +3445,15 @@
         <v>247</v>
       </c>
       <c r="C248" s="16" t="n">
-        <v>1057</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="11" t="n">
-        <v>458</v>
+      <c r="C249" s="16" t="n">
+        <v>1798</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3707,23 +3461,23 @@
         <v>249</v>
       </c>
       <c r="C250" s="16" t="n">
-        <v>1443</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="11" t="n">
-        <v>7</v>
+      <c r="C251" s="16" t="n">
+        <v>1708</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="11" t="n">
-        <v>495</v>
+      <c r="C252" s="16" t="n">
+        <v>1447</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3731,7 +3485,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="16" t="n">
-        <v>2698</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3739,15 +3493,15 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="255" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B255" s="15" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="255" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B255" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="11" t="n">
-        <v>216</v>
+      <c r="C255" s="12" t="n">
+        <v>2364</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3755,7 +3509,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>246</v>
+        <v>140</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3763,7 +3517,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>746</v>
+        <v>15</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3771,7 +3525,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>511</v>
+        <v>248</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3779,7 +3533,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>26</v>
+        <v>169</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3787,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3795,15 +3549,15 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>632</v>
+        <v>77</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="16" t="n">
-        <v>1457</v>
+      <c r="C262" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3811,7 +3565,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>709</v>
+        <v>89</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3819,7 +3573,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>344</v>
+        <v>258</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3827,7 +3581,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>652</v>
+        <v>177</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3835,7 +3589,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>276</v>
+        <v>353</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3843,7 +3597,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>557</v>
+        <v>27</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3851,7 +3605,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>636</v>
+        <v>121</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3859,39 +3613,39 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>293</v>
+        <v>12</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="16" t="n">
-        <v>1362</v>
+      <c r="C270" s="11" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="16" t="n">
-        <v>2379</v>
+      <c r="C271" s="11" t="n">
+        <v>239</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="16" t="n">
-        <v>2257</v>
-      </c>
-    </row>
-    <row r="273" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B273" s="15" t="s">
+      <c r="C272" s="11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="273" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B273" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="11" t="n">
-        <v>242</v>
+      <c r="C273" s="12" t="n">
+        <v>21575</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3899,7 +3653,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>62</v>
+        <v>426</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3907,7 +3661,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3915,7 +3669,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>925</v>
+        <v>195</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3923,23 +3677,23 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>462</v>
+        <v>85</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="16" t="n">
-        <v>2015</v>
+      <c r="C278" s="11" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="16" t="n">
-        <v>1877</v>
+      <c r="C279" s="11" t="n">
+        <v>305</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3947,15 +3701,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="281" ht="11" customHeight="true" outlineLevel="3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="281" ht="22" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="16" t="n">
-        <v>2636</v>
+      <c r="C281" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3963,15 +3717,15 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="283" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B283" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="283" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="12" t="n">
-        <v>4608</v>
+      <c r="C283" s="11" t="n">
+        <v>242</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3979,7 +3733,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>880</v>
+        <v>164</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3987,7 +3741,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>128</v>
+        <v>786</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3995,71 +3749,71 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="287" ht="11" customHeight="true" outlineLevel="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="287" ht="22" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="289" ht="11" customHeight="true" outlineLevel="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289" ht="22" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="290" ht="22" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="291" ht="11" customHeight="true" outlineLevel="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="291" ht="22" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="292" ht="11" customHeight="true" outlineLevel="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="292" ht="22" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="293" ht="11" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" ht="22" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="294" ht="11" customHeight="true" outlineLevel="3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="294" ht="22" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>161</v>
+        <v>50</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -4067,7 +3821,7 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>272</v>
+        <v>246</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -4075,7 +3829,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>508</v>
+        <v>176</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -4083,23 +3837,23 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>424</v>
+        <v>133</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="11" t="n">
-        <v>3</v>
+      <c r="C298" s="16" t="n">
+        <v>2046</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="11" t="n">
-        <v>17</v>
+      <c r="C299" s="16" t="n">
+        <v>2800</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -4107,31 +3861,31 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B301" s="14" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="12" t="n">
-        <v>21329</v>
+      <c r="C301" s="16" t="n">
+        <v>1368</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="C302" s="11" t="n">
-        <v>232</v>
+      <c r="C302" s="16" t="n">
+        <v>1485</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="11" t="n">
-        <v>199</v>
+      <c r="C303" s="16" t="n">
+        <v>2593</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4139,31 +3893,31 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>284</v>
+        <v>880</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="11" t="n">
-        <v>307</v>
+      <c r="C305" s="16" t="n">
+        <v>1014</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="307" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B307" s="15" t="s">
+      <c r="C306" s="16" t="n">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="307" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B307" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="11" t="n">
-        <v>324</v>
+      <c r="C307" s="12" t="n">
+        <v>30172</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4171,7 +3925,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>78</v>
+        <v>622</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -4179,7 +3933,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>336</v>
+        <v>400</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -4187,31 +3941,31 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="311" ht="11" customHeight="true" outlineLevel="3">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="311" ht="22" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="312" ht="11" customHeight="true" outlineLevel="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="true" outlineLevel="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>150</v>
+        <v>292</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
@@ -4219,7 +3973,7 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>247</v>
+        <v>572</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -4227,15 +3981,15 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>238</v>
+        <v>571</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="C316" s="11" t="n">
-        <v>438</v>
+      <c r="C316" s="16" t="n">
+        <v>1945</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4243,7 +3997,7 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>874</v>
+        <v>500</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4251,7 +4005,7 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4259,95 +4013,95 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="320" ht="22" customHeight="true" outlineLevel="3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="321" ht="22" customHeight="true" outlineLevel="3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="323" ht="22" customHeight="true" outlineLevel="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="324" ht="22" customHeight="true" outlineLevel="3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="325" ht="22" customHeight="true" outlineLevel="3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="326" ht="22" customHeight="true" outlineLevel="3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="327" ht="22" customHeight="true" outlineLevel="3">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="328" ht="22" customHeight="true" outlineLevel="3">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="329" ht="22" customHeight="true" outlineLevel="3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>52</v>
+        <v>300</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="11" t="n">
-        <v>153</v>
+      <c r="C330" s="16" t="n">
+        <v>1081</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4355,7 +4109,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>91</v>
+        <v>848</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4363,47 +4117,47 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="333" ht="22" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="334" ht="22" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>227</v>
+        <v>120</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="16" t="n">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="336" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C335" s="11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="336" ht="11" customHeight="true" outlineLevel="3">
       <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="337" ht="22" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="16" t="n">
-        <v>1734</v>
+      <c r="C337" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4411,31 +4165,31 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>349</v>
+        <v>410</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="16" t="n">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C340" s="11" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="341" ht="22" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>20</v>
+        <v>161</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4443,15 +4197,15 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="343" ht="11" customHeight="true" outlineLevel="3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="343" ht="22" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="16" t="n">
-        <v>1447</v>
+      <c r="C343" s="11" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4459,7 +4213,7 @@
         <v>343</v>
       </c>
       <c r="C344" s="16" t="n">
-        <v>4394</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4467,7 +4221,7 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>818</v>
+        <v>500</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4475,87 +4229,87 @@
         <v>345</v>
       </c>
       <c r="C346" s="16" t="n">
-        <v>1213</v>
+        <v>6531</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B348" s="14" t="s">
+      <c r="C347" s="16" t="n">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="17" t="n">
-        <v>46</v>
+      <c r="C348" s="16" t="n">
+        <v>1210</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B349" s="18" t="s">
+      <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="C349" s="17" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B350" s="19" t="s">
+      <c r="C349" s="11" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B350" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B351" s="19" t="s">
+      <c r="C350" s="17" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B352" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B353" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="354" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B354" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B354" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="12" t="n">
-        <v>16210</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B355" s="15" t="s">
+      <c r="C354" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B355" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="16" t="n">
-        <v>1240</v>
+      <c r="C355" s="12" t="n">
+        <v>11783</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="16" t="n">
-        <v>1602</v>
+      <c r="C356" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4563,7 +4317,7 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="358" ht="22" customHeight="true" outlineLevel="3">
@@ -4571,39 +4325,39 @@
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="359" ht="22" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="360" ht="22" customHeight="true" outlineLevel="3">
       <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="361" ht="22" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="362" ht="22" customHeight="true" outlineLevel="3">
       <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>116</v>
+        <v>12</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4611,7 +4365,7 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>237</v>
+        <v>334</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4619,31 +4373,31 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="365" ht="11" customHeight="true" outlineLevel="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="365" ht="22" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="366" ht="11" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="367" ht="11" customHeight="true" outlineLevel="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="367" ht="22" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>785</v>
+        <v>10</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4651,7 +4405,7 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>145</v>
+        <v>615</v>
       </c>
     </row>
     <row r="369" ht="11" customHeight="true" outlineLevel="3">
@@ -4659,7 +4413,7 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="370" ht="11" customHeight="true" outlineLevel="3">
@@ -4667,79 +4421,79 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="371" ht="22" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="372" ht="22" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="374" ht="22" customHeight="true" outlineLevel="3">
       <c r="B374" s="15" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="375" ht="22" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="376" ht="22" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="11" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C376" s="16" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="377" ht="22" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="378" ht="22" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="379" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C378" s="16" t="n">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="379" ht="22" customHeight="true" outlineLevel="3">
       <c r="B379" s="15" t="s">
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>300</v>
+        <v>101</v>
       </c>
     </row>
     <row r="380" ht="22" customHeight="true" outlineLevel="3">
@@ -4747,111 +4501,111 @@
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="381" ht="11" customHeight="true" outlineLevel="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="381" ht="22" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="382" ht="11" customHeight="true" outlineLevel="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="382" ht="22" customHeight="true" outlineLevel="3">
       <c r="B382" s="15" t="s">
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="383" ht="22" customHeight="true" outlineLevel="3">
       <c r="B383" s="15" t="s">
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="384" ht="11" customHeight="true" outlineLevel="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="384" ht="22" customHeight="true" outlineLevel="3">
       <c r="B384" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="C384" s="11" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C384" s="16" t="n">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="385" ht="22" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="387" ht="11" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="387" ht="22" customHeight="true" outlineLevel="3">
       <c r="B387" s="15" t="s">
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388" ht="11" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="16" t="n">
-        <v>1104</v>
+      <c r="C388" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="C389" s="16" t="n">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C389" s="11" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="390" ht="22" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="391" ht="11" customHeight="true" outlineLevel="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="391" ht="22" customHeight="true" outlineLevel="3">
       <c r="B391" s="15" t="s">
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="392" ht="11" customHeight="true" outlineLevel="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="392" ht="22" customHeight="true" outlineLevel="3">
       <c r="B392" s="15" t="s">
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="393" ht="11" customHeight="true" outlineLevel="3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="393" ht="22" customHeight="true" outlineLevel="3">
       <c r="B393" s="15" t="s">
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>175</v>
+        <v>18</v>
       </c>
     </row>
     <row r="394" ht="11" customHeight="true" outlineLevel="3">
@@ -4859,15 +4613,15 @@
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B395" s="14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="395" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="C395" s="17" t="n">
-        <v>281</v>
+      <c r="C395" s="11" t="n">
+        <v>542</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
@@ -4875,7 +4629,7 @@
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="397" ht="11" customHeight="true" outlineLevel="3">
@@ -4883,7 +4637,7 @@
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>108</v>
+        <v>19</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
@@ -4891,15 +4645,15 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B399" s="14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="399" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B399" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="C399" s="12" t="n">
-        <v>48820</v>
+      <c r="C399" s="11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="400" ht="11" customHeight="true" outlineLevel="3">
@@ -4907,7 +4661,7 @@
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
     </row>
     <row r="401" ht="11" customHeight="true" outlineLevel="3">
@@ -4915,7 +4669,7 @@
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>143</v>
+        <v>562</v>
       </c>
     </row>
     <row r="402" ht="22" customHeight="true" outlineLevel="3">
@@ -4923,687 +4677,47 @@
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="403" ht="22" customHeight="true" outlineLevel="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="403" ht="11" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="404" ht="33" customHeight="true" outlineLevel="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="404" ht="11" customHeight="true" outlineLevel="3">
       <c r="B404" s="15" t="s">
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="405" ht="22" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="3">
       <c r="B405" s="15" t="s">
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="406" ht="22" customHeight="true" outlineLevel="3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="3">
       <c r="B406" s="15" t="s">
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="407" ht="22" customHeight="true" outlineLevel="3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="3">
       <c r="B407" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="C407" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="408" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B408" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="C408" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B409" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="C409" s="11" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="410" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B410" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C410" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="411" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B411" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="C411" s="16" t="n">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="412" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B412" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="C412" s="11" t="n">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="413" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B413" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="C413" s="11" t="n">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="414" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B414" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C414" s="16" t="n">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="415" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B415" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="C415" s="11" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="416" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B416" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="C416" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="417" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B417" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="C417" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="418" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B418" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="C418" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="419" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B419" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="C419" s="16" t="n">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="420" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B420" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C420" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="421" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B421" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="C421" s="11" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="422" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B422" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="C422" s="11" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="423" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B423" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="C423" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="424" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B424" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="C424" s="11" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="425" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B425" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="C425" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="426" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B426" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="C426" s="16" t="n">
-        <v>3077</v>
-      </c>
-    </row>
-    <row r="427" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B427" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="C427" s="11" t="n">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="428" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B428" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="C428" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="429" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B429" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="C429" s="11" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="430" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B430" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="C430" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="431" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B431" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="C431" s="11" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="432" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B432" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="C432" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="433" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B433" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="C433" s="11" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="434" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B434" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="C434" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="435" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B435" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="C435" s="11" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="436" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B436" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="C436" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="437" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B437" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="C437" s="11" t="n">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="438" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B438" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="C438" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="439" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B439" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C439" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="440" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B440" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="C440" s="11" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="441" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B441" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="C441" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="442" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B442" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="C442" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="443" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B443" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="C443" s="11" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="444" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B444" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="C444" s="11" t="n">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="445" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B445" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="C445" s="11" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="446" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B446" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="C446" s="11" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="447" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B447" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="C447" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="448" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B448" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="C448" s="11" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="449" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B449" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="C449" s="11" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="450" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B450" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="C450" s="11" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="451" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B451" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="C451" s="11" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="452" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B452" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="C452" s="11" t="n">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="453" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B453" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="C453" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="454" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B454" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="C454" s="11" t="n">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="455" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B455" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="C455" s="11" t="n">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="456" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B456" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="C456" s="11" t="n">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="457" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B457" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="C457" s="11" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="458" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B458" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="C458" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="459" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B459" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="C459" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="460" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B460" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="C460" s="16" t="n">
-        <v>6338</v>
-      </c>
-    </row>
-    <row r="461" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B461" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="C461" s="11" t="n">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="462" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B462" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="C462" s="11" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="463" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B463" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="C463" s="16" t="n">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="464" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B464" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="C464" s="11" t="n">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="465" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B465" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="C465" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="466" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B466" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="C466" s="16" t="n">
-        <v>1544</v>
-      </c>
-    </row>
-    <row r="467" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B467" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="C467" s="11" t="n">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="468" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B468" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="C468" s="11" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="469" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B469" s="15" t="s">
-        <v>468</v>
-      </c>
-      <c r="C469" s="16" t="n">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="470" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B470" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="C470" s="16" t="n">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="471" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B471" s="15" t="s">
-        <v>470</v>
-      </c>
-      <c r="C471" s="11" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="472" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B472" s="15" t="s">
-        <v>471</v>
-      </c>
-      <c r="C472" s="16" t="n">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="473" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B473" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="C473" s="11" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="474" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B474" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="C474" s="11" t="n">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="475" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B475" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="C475" s="16" t="n">
-        <v>3304</v>
-      </c>
-    </row>
-    <row r="476" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B476" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="C476" s="16" t="n">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="477" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B477" s="15" t="s">
-        <v>476</v>
-      </c>
-      <c r="C477" s="11" t="n">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="478" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B478" s="15" t="s">
-        <v>477</v>
-      </c>
-      <c r="C478" s="11" t="n">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="479" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B479" s="15" t="s">
-        <v>478</v>
-      </c>
-      <c r="C479" s="11" t="n">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="480" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B480" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="C480" s="12" t="n">
-        <v>4369</v>
-      </c>
-    </row>
-    <row r="481" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B481" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="C481" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="482" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B482" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="C482" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="483" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B483" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="C483" s="11" t="n">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="484" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B484" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="C484" s="16" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="485" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B485" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="C485" s="16" t="n">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="486" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B486" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="C486" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="487" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B487" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="C487" s="11" t="n">
-        <v>18</v>
+      <c r="C407" s="16" t="n">
+        <v>1561</v>
       </c>
     </row>
   </sheetData>
